--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8484848484848485</v>
+        <v>0.84375</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3661971830985916</v>
+        <v>0.3591549295774648</v>
       </c>
       <c r="D2">
-        <v>0.7627118644067796</v>
+        <v>0.7711864406779662</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G2">
         <v>24</v>
